--- a/mobility-service/mobility-service.xlsx
+++ b/mobility-service/mobility-service.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BFFDBD-C082-4A30-AB55-F6AF4F5393FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164AC35-0BB7-44D5-9A85-D3ADCA459400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Refactor Proposal" sheetId="3" state="hidden" r:id="rId1"/>
@@ -1301,9 +1301,6 @@
     <t>Service for requesting point-to-point transport on demand via an application (e.g., Uber, Lyft, Bolt, etc.)</t>
   </si>
   <si>
-    <t>NAPCORE WG4 Task 4.4</t>
-  </si>
-  <si>
     <t>Ed Ooms (NDW)</t>
   </si>
   <si>
@@ -1319,10 +1316,13 @@
     <t>Peter Lubrich (BASt)</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>skos:narrower</t>
+  </si>
+  <si>
+    <t>NAPCORE Task 4.4</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
   </si>
 </sst>
 </file>
@@ -1854,13 +1854,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>21</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>29</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>31</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>33</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>35</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>47</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>51</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>54</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>59</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>61</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>63</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>66</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>68</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>70</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -2153,17 +2153,17 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B35" s="6"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B36" s="6"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>74</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>76</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>78</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>80</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>82</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>84</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>86</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>88</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>90</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>92</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>94</v>
       </c>
@@ -2251,19 +2251,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="11"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="11"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>96</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>99</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>101</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>103</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>106</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>108</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>110</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>112</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>114</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>116</v>
       </c>
@@ -2361,14 +2361,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDCB3D0-B550-4EFC-8834-EEEBF03CEB3D}">
   <dimension ref="A1:E92"/>
-  <sheetFormatPr defaultColWidth="55.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="55.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="72.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>119</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>120</v>
       </c>
@@ -2388,7 +2388,7 @@
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>122</v>
       </c>
@@ -2399,7 +2399,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>124</v>
       </c>
@@ -2410,7 +2410,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>126</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>128</v>
       </c>
@@ -2432,7 +2432,7 @@
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>130</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>46</v>
       </c>
@@ -2454,7 +2454,7 @@
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>133</v>
       </c>
@@ -2465,14 +2465,14 @@
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>120</v>
       </c>
@@ -2481,7 +2481,7 @@
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>44</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>42</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>7</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>9</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>38</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>58</v>
       </c>
@@ -2583,14 +2583,14 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>7</v>
       </c>
@@ -2599,7 +2599,7 @@
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>62</v>
       </c>
@@ -2625,14 +2625,14 @@
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>122</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>16</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
         <v>18</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>166</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>20</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>22</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>24</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>26</v>
       </c>
@@ -2760,14 +2760,14 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>124</v>
       </c>
@@ -2776,7 +2776,7 @@
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>182</v>
       </c>
@@ -2784,7 +2784,7 @@
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>183</v>
       </c>
@@ -2792,7 +2792,7 @@
       <c r="D34" s="19"/>
       <c r="E34" s="19"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>184</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="D35" s="19"/>
       <c r="E35" s="19"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>185</v>
       </c>
@@ -2808,7 +2808,7 @@
       <c r="D36" s="19"/>
       <c r="E36" s="19"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>186</v>
       </c>
@@ -2816,7 +2816,7 @@
       <c r="D37" s="19"/>
       <c r="E37" s="19"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>187</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>188</v>
       </c>
@@ -2832,7 +2832,7 @@
       <c r="D39" s="19"/>
       <c r="E39" s="19"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>189</v>
       </c>
@@ -2840,14 +2840,14 @@
       <c r="D40" s="19"/>
       <c r="E40" s="19"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="19"/>
       <c r="E41" s="19"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
         <v>126</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="D42" s="17"/>
       <c r="E42" s="17"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
         <v>190</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>32</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>30</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
         <v>64</v>
       </c>
@@ -2926,14 +2926,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="19"/>
       <c r="E47" s="17"/>
     </row>
-    <row r="48" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>128</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
         <v>34</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
         <v>67</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>69</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>36</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>71</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>220</v>
       </c>
@@ -3046,14 +3046,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
       <c r="D55" s="19"/>
       <c r="E55" s="17"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>130</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
         <v>40</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="17" t="s">
         <v>48</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
         <v>50</v>
       </c>
@@ -3115,14 +3115,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
       <c r="D60" s="19"/>
       <c r="E60" s="17"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>133</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>232</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>73</v>
       </c>
@@ -3167,14 +3167,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
     </row>
-    <row r="65" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="20" t="s">
         <v>241</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>243</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>247</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>251</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>255</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
         <v>259</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
         <v>262</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>266</v>
       </c>
@@ -3304,14 +3304,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
       <c r="D73" s="19"/>
       <c r="E73" s="17"/>
     </row>
-    <row r="74" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="20" t="s">
         <v>269</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="D74" s="19"/>
       <c r="E74" s="17"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>91</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="D75" s="19"/>
       <c r="E75" s="17"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>93</v>
       </c>
@@ -3344,7 +3344,7 @@
       <c r="D76" s="19"/>
       <c r="E76" s="17"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="17" t="s">
         <v>95</v>
       </c>
@@ -3355,14 +3355,14 @@
       <c r="D77" s="19"/>
       <c r="E77" s="17"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="17"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
       <c r="D78" s="19"/>
       <c r="E78" s="17"/>
     </row>
-    <row r="79" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="20" t="s">
         <v>274</v>
       </c>
@@ -3373,7 +3373,7 @@
       <c r="D79" s="17"/>
       <c r="E79" s="17"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="17" t="s">
         <v>97</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="17" t="s">
         <v>100</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="17" t="s">
         <v>102</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="17" t="s">
         <v>109</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="17" t="s">
         <v>107</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="17" t="s">
         <v>104</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="17" t="s">
         <v>111</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="17" t="s">
         <v>113</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="17" t="s">
         <v>304</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="17" t="s">
         <v>307</v>
       </c>
@@ -3543,21 +3543,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="17"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
       <c r="E90" s="17"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="17"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
       <c r="E91" s="17"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="17"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -3573,19 +3573,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC06747A-1FA3-4B2B-9F81-4ACDA7C45AF8}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="75.28515625" customWidth="1"/>
+    <col min="1" max="1" width="75.33203125" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="45.109375" style="23" customWidth="1"/>
     <col min="4" max="4" width="76" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" customWidth="1"/>
-    <col min="8" max="8" width="55.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.44140625" customWidth="1"/>
+    <col min="8" max="8" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>311</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>313</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>315</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>317</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>317</v>
       </c>
@@ -3625,63 +3625,63 @@
         <v>319</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="B7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>321</v>
       </c>
       <c r="B11" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B12" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>323</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>325</v>
       </c>
@@ -3698,13 +3698,13 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/1.0.0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>327</v>
       </c>
@@ -3712,15 +3712,15 @@
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>329</v>
       </c>
       <c r="B17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>330</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>333</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>334</v>
@@ -3746,7 +3746,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="str">
         <f t="shared" ref="A22:A39" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B22)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/sharing-mobility-service</v>
@@ -3763,7 +3763,7 @@
       <c r="G22" s="25"/>
       <c r="H22" s="24"/>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" ref="A23:A37" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B23)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/free-floating-sharing-service</v>
@@ -3779,7 +3779,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/sharing-mobility-service</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/station-based-sharing-service</v>
@@ -3795,7 +3795,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/sharing-mobility-service</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/ride-sharing</v>
@@ -3811,7 +3811,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/sharing-mobility-service</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/ride-pooling</v>
@@ -3827,7 +3827,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/sharing-mobility-service</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/hiring-mobility-service</v>
@@ -3839,7 +3839,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/rental-service</v>
@@ -3855,7 +3855,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/hiring-mobility-service</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/peer-to-peer</v>
@@ -3871,7 +3871,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/hiring-mobility-service</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
@@ -3883,7 +3883,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/scheduled</v>
@@ -3899,7 +3899,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/semi-scheduled</v>
@@ -3915,7 +3915,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/on-demand</v>
@@ -3931,7 +3931,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/fixed-route</v>
@@ -3947,7 +3947,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/flexible</v>
@@ -3963,7 +3963,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/door-to-door</v>
@@ -3979,7 +3979,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/shuttle-service</v>
@@ -3995,7 +3995,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/taxi</v>
@@ -4011,7 +4011,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/transport-service</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-service/ride-hailing</v>
@@ -4039,14 +4039,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4251,21 +4249,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
-    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4290,9 +4287,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>